--- a/base_prov/ml/ml_abbott_2026-07-13.xlsx
+++ b/base_prov/ml/ml_abbott_2026-07-13.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\como se me cante\retail-chatbot-main\eci_abbott-main\base_prov\ml\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{453400F5-0460-4B5D-B53B-4470E5C82C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D59C6B-B6C7-4AE3-8EB7-CDF95956080A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -491,7 +491,7 @@
     <t>https://www.mercadolibre.com.mx/pack-x16-bebidas-advance-sabor-chocolate-3792ml-ensure/p/MLM20775721#polycard_client=search-desktop&amp;be_origin=backend&amp;search_layout=grid&amp;position=2&amp;type=product&amp;tracking_id=d6c00af2-3145-4359-9435-56cb7ab21902&amp;wid=MLM3071871127&amp;sid=search</t>
   </si>
   <si>
-    <t>2026-07-08</t>
+    <t>2026-07-13</t>
   </si>
 </sst>
 </file>
@@ -547,12 +547,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -914,7 +913,7 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>152</v>
       </c>
       <c r="B2" t="s">
@@ -955,7 +954,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
         <v>152</v>
       </c>
       <c r="B3" t="s">
@@ -996,7 +995,7 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+      <c r="A4" t="s">
         <v>152</v>
       </c>
       <c r="B4" t="s">
@@ -1037,7 +1036,7 @@
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+      <c r="A5" t="s">
         <v>152</v>
       </c>
       <c r="B5" t="s">
@@ -1078,7 +1077,7 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+      <c r="A6" t="s">
         <v>152</v>
       </c>
       <c r="B6" t="s">
@@ -1119,7 +1118,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
+      <c r="A7" t="s">
         <v>152</v>
       </c>
       <c r="B7" t="s">
@@ -1160,7 +1159,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
+      <c r="A8" t="s">
         <v>152</v>
       </c>
       <c r="B8" t="s">
@@ -1201,7 +1200,7 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
+      <c r="A9" t="s">
         <v>152</v>
       </c>
       <c r="B9" t="s">
@@ -1242,7 +1241,7 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
+      <c r="A10" t="s">
         <v>152</v>
       </c>
       <c r="B10" t="s">
@@ -1283,7 +1282,7 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
+      <c r="A11" t="s">
         <v>152</v>
       </c>
       <c r="B11" t="s">
@@ -1324,7 +1323,7 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
+      <c r="A12" t="s">
         <v>152</v>
       </c>
       <c r="B12" t="s">
@@ -1365,7 +1364,7 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
+      <c r="A13" t="s">
         <v>152</v>
       </c>
       <c r="B13" t="s">
@@ -1406,7 +1405,7 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
+      <c r="A14" t="s">
         <v>152</v>
       </c>
       <c r="B14" t="s">
@@ -1447,7 +1446,7 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
+      <c r="A15" t="s">
         <v>152</v>
       </c>
       <c r="B15" t="s">
@@ -1488,7 +1487,7 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
+      <c r="A16" t="s">
         <v>152</v>
       </c>
       <c r="B16" t="s">
@@ -1529,7 +1528,7 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
+      <c r="A17" t="s">
         <v>152</v>
       </c>
       <c r="B17" t="s">
@@ -1570,7 +1569,7 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A18" s="2" t="s">
+      <c r="A18" t="s">
         <v>152</v>
       </c>
       <c r="B18" t="s">
@@ -1611,7 +1610,7 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A19" s="2" t="s">
+      <c r="A19" t="s">
         <v>152</v>
       </c>
       <c r="B19" t="s">
@@ -1652,7 +1651,7 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
+      <c r="A20" t="s">
         <v>152</v>
       </c>
       <c r="B20" t="s">
@@ -1693,7 +1692,7 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A21" s="2" t="s">
+      <c r="A21" t="s">
         <v>152</v>
       </c>
       <c r="B21" t="s">
@@ -1734,7 +1733,7 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A22" s="2" t="s">
+      <c r="A22" t="s">
         <v>152</v>
       </c>
       <c r="B22" t="s">
@@ -1775,7 +1774,7 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A23" s="2" t="s">
+      <c r="A23" t="s">
         <v>152</v>
       </c>
       <c r="B23" t="s">
@@ -1816,7 +1815,7 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A24" s="2" t="s">
+      <c r="A24" t="s">
         <v>152</v>
       </c>
       <c r="B24" t="s">
@@ -1857,7 +1856,7 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A25" s="2" t="s">
+      <c r="A25" t="s">
         <v>152</v>
       </c>
       <c r="B25" t="s">
@@ -1898,7 +1897,7 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A26" s="2" t="s">
+      <c r="A26" t="s">
         <v>152</v>
       </c>
       <c r="B26" t="s">
@@ -1939,7 +1938,7 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A27" s="2" t="s">
+      <c r="A27" t="s">
         <v>152</v>
       </c>
       <c r="B27" t="s">
@@ -1980,7 +1979,7 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A28" s="2" t="s">
+      <c r="A28" t="s">
         <v>152</v>
       </c>
       <c r="B28" t="s">
@@ -2021,7 +2020,7 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A29" s="2" t="s">
+      <c r="A29" t="s">
         <v>152</v>
       </c>
       <c r="B29" t="s">
@@ -2062,7 +2061,7 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A30" s="2" t="s">
+      <c r="A30" t="s">
         <v>152</v>
       </c>
       <c r="B30" t="s">
@@ -2103,7 +2102,7 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A31" s="2" t="s">
+      <c r="A31" t="s">
         <v>152</v>
       </c>
       <c r="B31" t="s">
@@ -2144,7 +2143,7 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A32" s="2" t="s">
+      <c r="A32" t="s">
         <v>152</v>
       </c>
       <c r="B32" t="s">
@@ -2185,7 +2184,7 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A33" s="2" t="s">
+      <c r="A33" t="s">
         <v>152</v>
       </c>
       <c r="B33" t="s">
@@ -2226,7 +2225,7 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A34" s="2" t="s">
+      <c r="A34" t="s">
         <v>152</v>
       </c>
       <c r="B34" t="s">
@@ -2267,7 +2266,7 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A35" s="2" t="s">
+      <c r="A35" t="s">
         <v>152</v>
       </c>
       <c r="B35" t="s">
@@ -2308,7 +2307,7 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A36" s="2" t="s">
+      <c r="A36" t="s">
         <v>152</v>
       </c>
       <c r="B36" t="s">
@@ -2349,7 +2348,7 @@
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A37" s="2" t="s">
+      <c r="A37" t="s">
         <v>152</v>
       </c>
       <c r="B37" t="s">
@@ -2390,7 +2389,7 @@
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A38" s="2" t="s">
+      <c r="A38" t="s">
         <v>152</v>
       </c>
       <c r="B38" t="s">
@@ -2431,7 +2430,7 @@
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A39" s="2" t="s">
+      <c r="A39" t="s">
         <v>152</v>
       </c>
       <c r="B39" t="s">
@@ -2472,7 +2471,7 @@
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A40" s="2" t="s">
+      <c r="A40" t="s">
         <v>152</v>
       </c>
       <c r="B40" t="s">
@@ -2513,7 +2512,7 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A41" s="2" t="s">
+      <c r="A41" t="s">
         <v>152</v>
       </c>
       <c r="B41" t="s">
@@ -2554,7 +2553,7 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A42" s="2" t="s">
+      <c r="A42" t="s">
         <v>152</v>
       </c>
       <c r="B42" t="s">
@@ -2595,7 +2594,7 @@
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A43" s="2" t="s">
+      <c r="A43" t="s">
         <v>152</v>
       </c>
       <c r="B43" t="s">
@@ -2636,7 +2635,7 @@
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A44" s="2" t="s">
+      <c r="A44" t="s">
         <v>152</v>
       </c>
       <c r="B44" t="s">
@@ -2677,7 +2676,7 @@
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A45" s="2" t="s">
+      <c r="A45" t="s">
         <v>152</v>
       </c>
       <c r="B45" t="s">
@@ -2718,7 +2717,7 @@
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A46" s="2" t="s">
+      <c r="A46" t="s">
         <v>152</v>
       </c>
       <c r="B46" t="s">
@@ -2759,7 +2758,7 @@
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A47" s="2" t="s">
+      <c r="A47" t="s">
         <v>152</v>
       </c>
       <c r="B47" t="s">
@@ -2800,7 +2799,7 @@
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A48" s="2" t="s">
+      <c r="A48" t="s">
         <v>152</v>
       </c>
       <c r="B48" t="s">
@@ -2841,7 +2840,7 @@
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A49" s="2" t="s">
+      <c r="A49" t="s">
         <v>152</v>
       </c>
       <c r="B49" t="s">
@@ -2882,7 +2881,7 @@
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A50" s="2" t="s">
+      <c r="A50" t="s">
         <v>152</v>
       </c>
       <c r="B50" t="s">
@@ -2923,7 +2922,7 @@
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A51" s="2" t="s">
+      <c r="A51" t="s">
         <v>152</v>
       </c>
       <c r="B51" t="s">
@@ -2964,7 +2963,7 @@
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A52" s="2" t="s">
+      <c r="A52" t="s">
         <v>152</v>
       </c>
       <c r="B52" t="s">
@@ -3005,7 +3004,7 @@
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A53" s="2" t="s">
+      <c r="A53" t="s">
         <v>152</v>
       </c>
       <c r="B53" t="s">
@@ -3046,7 +3045,7 @@
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A54" s="2" t="s">
+      <c r="A54" t="s">
         <v>152</v>
       </c>
       <c r="B54" t="s">
@@ -3087,7 +3086,7 @@
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A55" s="2" t="s">
+      <c r="A55" t="s">
         <v>152</v>
       </c>
       <c r="B55" t="s">
@@ -3128,7 +3127,7 @@
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A56" s="2" t="s">
+      <c r="A56" t="s">
         <v>152</v>
       </c>
       <c r="B56" t="s">
@@ -3169,7 +3168,7 @@
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A57" s="2" t="s">
+      <c r="A57" t="s">
         <v>152</v>
       </c>
       <c r="B57" t="s">
@@ -3210,7 +3209,7 @@
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A58" s="2" t="s">
+      <c r="A58" t="s">
         <v>152</v>
       </c>
       <c r="B58" t="s">
@@ -3251,7 +3250,7 @@
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A59" s="2" t="s">
+      <c r="A59" t="s">
         <v>152</v>
       </c>
       <c r="B59" t="s">
@@ -3292,7 +3291,7 @@
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A60" s="2" t="s">
+      <c r="A60" t="s">
         <v>152</v>
       </c>
       <c r="B60" t="s">
@@ -3333,7 +3332,7 @@
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A61" s="2" t="s">
+      <c r="A61" t="s">
         <v>152</v>
       </c>
       <c r="B61" t="s">
@@ -3374,7 +3373,7 @@
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A62" s="2" t="s">
+      <c r="A62" t="s">
         <v>152</v>
       </c>
       <c r="B62" t="s">
@@ -3415,7 +3414,7 @@
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A63" s="2" t="s">
+      <c r="A63" t="s">
         <v>152</v>
       </c>
       <c r="B63" t="s">
@@ -3456,7 +3455,7 @@
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A64" s="2" t="s">
+      <c r="A64" t="s">
         <v>152</v>
       </c>
       <c r="B64" t="s">
@@ -3497,7 +3496,7 @@
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A65" s="2" t="s">
+      <c r="A65" t="s">
         <v>152</v>
       </c>
       <c r="B65" t="s">

--- a/base_prov/ml/ml_abbott_2026-07-13.xlsx
+++ b/base_prov/ml/ml_abbott_2026-07-13.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\como se me cante\retail-chatbot-main\eci_abbott-main\base_prov\ml\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D59C6B-B6C7-4AE3-8EB7-CDF95956080A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C14FC663-F701-483A-8AD7-5B43EFEACA1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -452,9 +452,6 @@
     <t>https://www.mercadolibre.com.mx/similac-ar-350-gr/p/MLM36975271?pdp_filters=shipping%3Afulfillment%7Cdeal%3AMLM1020488-1#polycard_client=search-desktop&amp;be_origin=backend&amp;search_layout=grid&amp;position=1&amp;type=product&amp;tracking_id=4c08bcd3-c7f0-4dba-b0c7-7e01ba0cffab&amp;wid=MLM2261248051&amp;sid=search</t>
   </si>
   <si>
-    <t>https://www.mercadolibre.com.mx/formula-infantil-similac-isomil-etapa-1-de-soya-850gr-natural/p/MLM15186216?pdp_filters=shipping%3Afulfillment%7Cdeal%3AMLM1020488-1#polycard_client=search-desktop&amp;be_origin=backend&amp;search_layout=grid&amp;position=2&amp;type=product&amp;tracking_id=faf46c5f-aa8b-434a-ace5-4f33b5e91af9&amp;wid=MLM2941046703&amp;sid=search</t>
-  </si>
-  <si>
     <t>https://www.mercadolibre.com.mx/formula-infantil-sabor-natural-etapa-2-en-lata-350-g-similac/p/MLM50744579#polycard_client=search-desktop&amp;be_origin=backend&amp;search_layout=grid&amp;position=1&amp;type=product&amp;tracking_id=39358edb-aa00-42cc-b539-56b6d18a2c95&amp;wid=MLM2434486579&amp;sid=search</t>
   </si>
   <si>
@@ -479,9 +476,6 @@
     <t>https://www.mercadolibre.com.mx/suplemento-en-polvo-ensure-sabor-vainilla-en-lata-de-400g/p/MLM18564592#polycard_client=search-desktop&amp;be_origin=backend&amp;search_layout=grid&amp;position=1&amp;type=product&amp;tracking_id=73764457-9831-4db8-b84c-d9ace097c39d&amp;wid=MLM1487412130&amp;sid=search</t>
   </si>
   <si>
-    <t>https://www.mercadolibre.com.mx/similac-total-comfort-1-350-gr/p/MLM37793430?pdp_filters=shipping%3Afulfillment%7Cdeal%3AMLM1020488-1#polycard_client=search-desktop&amp;be_origin=backend&amp;search_layout=grid&amp;position=1&amp;type=product&amp;tracking_id=0a531053-707a-4b99-bad1-cf75f1fd4cdc&amp;wid=MLM2261338395&amp;sid=search</t>
-  </si>
-  <si>
     <t>Farmacia Prixz</t>
   </si>
   <si>
@@ -492,6 +486,12 @@
   </si>
   <si>
     <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/similac-total-comfort-1-350-gr/p/MLM37793430?pdp_filters=deal%3AMLM1020488-1%7Cshipping%3Afulfillment#polycard_client=search-desktop&amp;be_origin=backend&amp;search_layout=grid&amp;position=1&amp;type=product&amp;tracking_id=af55b372-b95d-42f1-a646-71d83e5c4087&amp;wid=MLM5333710710&amp;sid=search</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/formula-infantil-similac-isomil-etapa-1-de-soya-850gr-natural/p/MLM15186216?pdp_filters=shipping%3Afulfillment%7Cdeal%3AMLM1020488-1#polycard_client=search-desktop&amp;be_origin=backend&amp;search_layout=grid&amp;position=1&amp;type=product&amp;tracking_id=45a88e41-5829-4f17-98c9-78d53401cb99&amp;wid=MLM1378980533&amp;sid=search</t>
   </si>
 </sst>
 </file>
@@ -914,7 +914,7 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
@@ -955,7 +955,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
@@ -973,10 +973,10 @@
         <v>11</v>
       </c>
       <c r="H3">
-        <v>813</v>
+        <v>835</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
@@ -1005,7 +1005,7 @@
         <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F4">
         <v>10000</v>
@@ -1014,7 +1014,7 @@
         <v>11</v>
       </c>
       <c r="H4">
-        <v>1645</v>
+        <v>1650</v>
       </c>
       <c r="I4">
         <v>2</v>
@@ -1037,7 +1037,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
@@ -1055,10 +1055,10 @@
         <v>11</v>
       </c>
       <c r="H5">
-        <v>812</v>
+        <v>835</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1078,7 +1078,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
@@ -1096,10 +1096,10 @@
         <v>11</v>
       </c>
       <c r="H6">
-        <v>812</v>
+        <v>835</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
@@ -1137,7 +1137,7 @@
         <v>11</v>
       </c>
       <c r="H7">
-        <v>799</v>
+        <v>809</v>
       </c>
       <c r="I7">
         <v>3</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
@@ -1178,7 +1178,7 @@
         <v>11</v>
       </c>
       <c r="H8">
-        <v>418</v>
+        <v>397</v>
       </c>
       <c r="I8">
         <v>3</v>
@@ -1201,7 +1201,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
@@ -1219,7 +1219,7 @@
         <v>11</v>
       </c>
       <c r="H9">
-        <v>1850</v>
+        <v>1901</v>
       </c>
       <c r="I9">
         <v>2</v>
@@ -1242,7 +1242,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
@@ -1260,7 +1260,7 @@
         <v>11</v>
       </c>
       <c r="H10">
-        <v>789</v>
+        <v>803</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -1283,7 +1283,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
@@ -1301,7 +1301,7 @@
         <v>11</v>
       </c>
       <c r="H11">
-        <v>1850</v>
+        <v>1901</v>
       </c>
       <c r="I11">
         <v>2</v>
@@ -1324,7 +1324,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
@@ -1342,7 +1342,7 @@
         <v>11</v>
       </c>
       <c r="H12">
-        <v>1850</v>
+        <v>1901</v>
       </c>
       <c r="I12">
         <v>4</v>
@@ -1357,7 +1357,7 @@
         <v>521</v>
       </c>
       <c r="M12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N12" t="s">
         <v>10</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B13" t="s">
         <v>15</v>
@@ -1383,7 +1383,7 @@
         <v>11</v>
       </c>
       <c r="H13">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="I13">
         <v>4</v>
@@ -1406,7 +1406,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
@@ -1424,7 +1424,7 @@
         <v>11</v>
       </c>
       <c r="H14">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="I14">
         <v>4</v>
@@ -1447,7 +1447,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B15" t="s">
         <v>15</v>
@@ -1465,7 +1465,7 @@
         <v>13</v>
       </c>
       <c r="H15">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="I15">
         <v>1</v>
@@ -1488,7 +1488,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B16" t="s">
         <v>15</v>
@@ -1506,7 +1506,7 @@
         <v>11</v>
       </c>
       <c r="H16">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="I16">
         <v>4</v>
@@ -1529,7 +1529,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B17" t="s">
         <v>15</v>
@@ -1547,7 +1547,7 @@
         <v>11</v>
       </c>
       <c r="H17">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="I17">
         <v>2</v>
@@ -1570,7 +1570,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B18" t="s">
         <v>15</v>
@@ -1588,7 +1588,7 @@
         <v>9</v>
       </c>
       <c r="H18">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -1611,7 +1611,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B19" t="s">
         <v>15</v>
@@ -1629,7 +1629,7 @@
         <v>13</v>
       </c>
       <c r="H19">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I19">
         <v>2</v>
@@ -1652,7 +1652,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B20" t="s">
         <v>15</v>
@@ -1693,7 +1693,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B21" t="s">
         <v>15</v>
@@ -1711,7 +1711,7 @@
         <v>13</v>
       </c>
       <c r="H21">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="I21">
         <v>1</v>
@@ -1734,7 +1734,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B22" t="s">
         <v>15</v>
@@ -1752,7 +1752,7 @@
         <v>13</v>
       </c>
       <c r="H22">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I22">
         <v>2</v>
@@ -1775,7 +1775,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B23" t="s">
         <v>15</v>
@@ -1793,7 +1793,7 @@
         <v>13</v>
       </c>
       <c r="H23">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I23">
         <v>2</v>
@@ -1816,7 +1816,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B24" t="s">
         <v>15</v>
@@ -1834,7 +1834,7 @@
         <v>11</v>
       </c>
       <c r="H24">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="I24">
         <v>2</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B25" t="s">
         <v>15</v>
@@ -1878,7 +1878,7 @@
         <v>80</v>
       </c>
       <c r="I25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -1898,7 +1898,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B26" t="s">
         <v>15</v>
@@ -1939,7 +1939,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B27" t="s">
         <v>15</v>
@@ -1980,7 +1980,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B28" t="s">
         <v>15</v>
@@ -1998,7 +1998,7 @@
         <v>11</v>
       </c>
       <c r="H28">
-        <v>1298</v>
+        <v>1336</v>
       </c>
       <c r="I28">
         <v>5</v>
@@ -2021,7 +2021,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B29" t="s">
         <v>15</v>
@@ -2030,7 +2030,7 @@
         <v>43</v>
       </c>
       <c r="E29" t="s">
-        <v>149</v>
+        <v>8</v>
       </c>
       <c r="F29">
         <v>10000</v>
@@ -2039,7 +2039,7 @@
         <v>11</v>
       </c>
       <c r="H29">
-        <v>2476</v>
+        <v>2499</v>
       </c>
       <c r="I29">
         <v>2</v>
@@ -2062,7 +2062,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B30" t="s">
         <v>15</v>
@@ -2071,7 +2071,7 @@
         <v>44</v>
       </c>
       <c r="E30" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F30">
         <v>1000</v>
@@ -2080,7 +2080,7 @@
         <v>11</v>
       </c>
       <c r="H30">
-        <v>1152</v>
+        <v>1163</v>
       </c>
       <c r="I30">
         <v>4</v>
@@ -2095,7 +2095,7 @@
         <v>1147</v>
       </c>
       <c r="M30" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="N30" t="s">
         <v>12</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B31" t="s">
         <v>15</v>
@@ -2121,7 +2121,7 @@
         <v>11</v>
       </c>
       <c r="H31">
-        <v>1298</v>
+        <v>1336</v>
       </c>
       <c r="I31">
         <v>5</v>
@@ -2144,7 +2144,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B32" t="s">
         <v>15</v>
@@ -2185,7 +2185,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B33" t="s">
         <v>15</v>
@@ -2203,7 +2203,7 @@
         <v>11</v>
       </c>
       <c r="H33">
-        <v>20214</v>
+        <v>20624</v>
       </c>
       <c r="I33">
         <v>11</v>
@@ -2226,7 +2226,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B34" t="s">
         <v>15</v>
@@ -2244,7 +2244,7 @@
         <v>11</v>
       </c>
       <c r="H34">
-        <v>2469</v>
+        <v>2517</v>
       </c>
       <c r="I34">
         <v>6</v>
@@ -2267,7 +2267,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B35" t="s">
         <v>15</v>
@@ -2285,7 +2285,7 @@
         <v>11</v>
       </c>
       <c r="H35">
-        <v>20251</v>
+        <v>20419</v>
       </c>
       <c r="I35">
         <v>12</v>
@@ -2300,7 +2300,7 @@
         <v>531</v>
       </c>
       <c r="M35" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N35" t="s">
         <v>10</v>
@@ -2308,7 +2308,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B36" t="s">
         <v>15</v>
@@ -2326,7 +2326,7 @@
         <v>11</v>
       </c>
       <c r="H36">
-        <v>20251</v>
+        <v>20419</v>
       </c>
       <c r="I36">
         <v>1</v>
@@ -2349,7 +2349,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B37" t="s">
         <v>15</v>
@@ -2390,7 +2390,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B38" t="s">
         <v>15</v>
@@ -2408,7 +2408,7 @@
         <v>11</v>
       </c>
       <c r="H38">
-        <v>1301</v>
+        <v>1336</v>
       </c>
       <c r="I38">
         <v>5</v>
@@ -2431,7 +2431,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B39" t="s">
         <v>15</v>
@@ -2449,7 +2449,7 @@
         <v>13</v>
       </c>
       <c r="H39">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I39">
         <v>2</v>
@@ -2472,7 +2472,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B40" t="s">
         <v>15</v>
@@ -2490,7 +2490,7 @@
         <v>11</v>
       </c>
       <c r="H40">
-        <v>2485</v>
+        <v>2499</v>
       </c>
       <c r="I40">
         <v>6</v>
@@ -2505,7 +2505,7 @@
         <v>698</v>
       </c>
       <c r="M40" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N40" t="s">
         <v>10</v>
@@ -2513,7 +2513,7 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B41" t="s">
         <v>15</v>
@@ -2531,7 +2531,7 @@
         <v>11</v>
       </c>
       <c r="H41">
-        <v>546</v>
+        <v>560</v>
       </c>
       <c r="I41">
         <v>1</v>
@@ -2554,7 +2554,7 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B42" t="s">
         <v>15</v>
@@ -2563,7 +2563,7 @@
         <v>56</v>
       </c>
       <c r="E42" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F42">
         <v>10000</v>
@@ -2572,7 +2572,7 @@
         <v>9</v>
       </c>
       <c r="H42">
-        <v>546</v>
+        <v>560</v>
       </c>
       <c r="I42">
         <v>5</v>
@@ -2587,7 +2587,7 @@
         <v>789</v>
       </c>
       <c r="M42" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="N42" t="s">
         <v>12</v>
@@ -2595,7 +2595,7 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B43" t="s">
         <v>15</v>
@@ -2613,7 +2613,7 @@
         <v>9</v>
       </c>
       <c r="H43">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="I43">
         <v>3</v>
@@ -2636,7 +2636,7 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B44" t="s">
         <v>15</v>
@@ -2654,7 +2654,7 @@
         <v>14</v>
       </c>
       <c r="H44">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I44">
         <v>2</v>
@@ -2677,7 +2677,7 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B45" t="s">
         <v>15</v>
@@ -2695,7 +2695,7 @@
         <v>11</v>
       </c>
       <c r="H45">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I45">
         <v>3</v>
@@ -2718,7 +2718,7 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B46" t="s">
         <v>15</v>
@@ -2736,7 +2736,7 @@
         <v>9</v>
       </c>
       <c r="H46">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="I46">
         <v>2</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B47" t="s">
         <v>15</v>
@@ -2800,7 +2800,7 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B48" t="s">
         <v>15</v>
@@ -2841,7 +2841,7 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B49" t="s">
         <v>15</v>
@@ -2882,7 +2882,7 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B50" t="s">
         <v>15</v>
@@ -2923,7 +2923,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B51" t="s">
         <v>15</v>
@@ -2935,13 +2935,13 @@
         <v>8</v>
       </c>
       <c r="F51">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="G51" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H51">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I51">
         <v>1</v>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B52" t="s">
         <v>15</v>
@@ -2979,10 +2979,10 @@
         <v>1000</v>
       </c>
       <c r="G52" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H52">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I52">
         <v>1</v>
@@ -3005,7 +3005,7 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B53" t="s">
         <v>15</v>
@@ -3023,7 +3023,7 @@
         <v>9</v>
       </c>
       <c r="H53">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I53">
         <v>6</v>
@@ -3046,7 +3046,7 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B54" t="s">
         <v>15</v>
@@ -3087,7 +3087,7 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B55" t="s">
         <v>15</v>
@@ -3105,7 +3105,7 @@
         <v>11</v>
       </c>
       <c r="H55">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="I55">
         <v>1</v>
@@ -3128,7 +3128,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B56" t="s">
         <v>15</v>
@@ -3146,7 +3146,7 @@
         <v>9</v>
       </c>
       <c r="H56">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I56">
         <v>1</v>
@@ -3169,7 +3169,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B57" t="s">
         <v>15</v>
@@ -3184,10 +3184,10 @@
         <v>500</v>
       </c>
       <c r="G57" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H57">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I57">
         <v>4</v>
@@ -3210,7 +3210,7 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B58" t="s">
         <v>15</v>
@@ -3251,7 +3251,7 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B59" t="s">
         <v>15</v>
@@ -3269,7 +3269,7 @@
         <v>9</v>
       </c>
       <c r="H59">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I59">
         <v>5</v>
@@ -3292,7 +3292,7 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B60" t="s">
         <v>15</v>
@@ -3301,7 +3301,7 @@
         <v>74</v>
       </c>
       <c r="E60" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F60">
         <v>1000</v>
@@ -3310,13 +3310,13 @@
         <v>9</v>
       </c>
       <c r="H60">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I60">
         <v>2</v>
       </c>
       <c r="J60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K60">
         <v>61</v>
@@ -3325,15 +3325,15 @@
         <v>780</v>
       </c>
       <c r="M60" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B61" t="s">
         <v>15</v>
@@ -3366,7 +3366,7 @@
         <v>1365</v>
       </c>
       <c r="M61" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N61" t="s">
         <v>10</v>
@@ -3374,7 +3374,7 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B62" t="s">
         <v>15</v>
@@ -3392,7 +3392,7 @@
         <v>9</v>
       </c>
       <c r="H62">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="I62">
         <v>2</v>
@@ -3407,7 +3407,7 @@
         <v>449</v>
       </c>
       <c r="M62" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N62" t="s">
         <v>10</v>
@@ -3415,7 +3415,7 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B63" t="s">
         <v>15</v>
@@ -3448,7 +3448,7 @@
         <v>606</v>
       </c>
       <c r="M63" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N63" t="s">
         <v>10</v>
@@ -3456,7 +3456,7 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B64" t="s">
         <v>15</v>
@@ -3474,7 +3474,7 @@
         <v>9</v>
       </c>
       <c r="H64">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="I64">
         <v>1</v>
@@ -3489,7 +3489,7 @@
         <v>583</v>
       </c>
       <c r="M64" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N64" t="s">
         <v>10</v>
@@ -3497,7 +3497,7 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B65" t="s">
         <v>15</v>
@@ -3515,7 +3515,7 @@
         <v>11</v>
       </c>
       <c r="H65">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I65">
         <v>4</v>
@@ -3530,7 +3530,7 @@
         <v>461</v>
       </c>
       <c r="M65" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N65" t="s">
         <v>10</v>
